--- a/组合实盘追踪/20260522_银河.xlsx
+++ b/组合实盘追踪/20260522_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>693.2</v>
+        <v>694.6</v>
       </c>
       <c r="D2" s="1">
-        <v>6.8</v>
+        <v>8.2</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0099</v>
+        <v>0.0119</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-17.9</v>
+        <v>-16.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0252</v>
+        <v>-0.0232</v>
       </c>
       <c r="L2" s="1">
-        <v>-17.9</v>
+        <v>-16.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0252</v>
+        <v>-0.0232</v>
       </c>
       <c r="N2" s="1">
-        <v>-8</v>
+        <v>-7.6</v>
       </c>
       <c r="O2" s="1">
-        <v>-21.5</v>
+        <v>-21.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-21.5</v>
+        <v>-21.1</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>10</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0099</v>
+        <v>0.0119</v>
       </c>
       <c r="U2" s="5">
-        <v>3.466</v>
+        <v>3.473</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.026</v>
+        <v>0.0239</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0365</v>
+        <v>0.0386</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.055</v>
+        <v>0.0572</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2261</v>
+        <v>0.2286</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4282</v>
+        <v>0.4311</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>829.2</v>
+        <v>830</v>
       </c>
       <c r="D3" s="1">
-        <v>-5.2</v>
+        <v>-4.4</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0062</v>
+        <v>-0.0053</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-33.7</v>
+        <v>-32.9</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0391</v>
+        <v>-0.0381</v>
       </c>
       <c r="L3" s="1">
-        <v>-33.7</v>
+        <v>-32.9</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0391</v>
+        <v>-0.0381</v>
       </c>
       <c r="N3" s="1">
-        <v>-5.2</v>
+        <v>-5.6</v>
       </c>
       <c r="O3" s="1">
-        <v>-32.5</v>
+        <v>-32.9</v>
       </c>
       <c r="P3" s="1">
-        <v>-32.5</v>
+        <v>-32.9</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -666,28 +666,28 @@
         <v>10</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0062</v>
+        <v>-0.0053</v>
       </c>
       <c r="U3" s="5">
-        <v>2.073</v>
+        <v>2.075</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0405</v>
+        <v>0.0395</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0254</v>
+        <v>-0.0245</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0365</v>
+        <v>0.0375</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0485</v>
+        <v>0.0495</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0736</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>695.2</v>
+        <v>698.5</v>
       </c>
       <c r="D4" s="1">
-        <v>5.5</v>
+        <v>8.8</v>
       </c>
       <c r="E4" s="2">
-        <v>0.008</v>
+        <v>0.0128</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-41.9</v>
+        <v>-38.6</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0524</v>
       </c>
       <c r="L4" s="1">
-        <v>-41.9</v>
+        <v>-38.6</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0569</v>
+        <v>-0.0524</v>
       </c>
       <c r="N4" s="1">
-        <v>-19.8</v>
+        <v>-20.9</v>
       </c>
       <c r="O4" s="1">
-        <v>-43</v>
+        <v>-44.1</v>
       </c>
       <c r="P4" s="1">
-        <v>-43</v>
+        <v>-44.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0238</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>10</v>
       </c>
       <c r="T4" s="2">
-        <v>0.008</v>
+        <v>0.0128</v>
       </c>
       <c r="U4" s="5">
-        <v>0.632</v>
+        <v>0.635</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0601</v>
+        <v>0.0551</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0511</v>
+        <v>-0.0466</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1259</v>
+        <v>-0.1217</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1584</v>
+        <v>-0.1544</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1425</v>
+        <v>-0.1384</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>966.8</v>
+        <v>968</v>
       </c>
       <c r="D5" s="1">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0054</v>
+        <v>0.0067</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-24.5</v>
+        <v>-23.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0235</v>
       </c>
       <c r="L5" s="1">
-        <v>-24.5</v>
+        <v>-23.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0235</v>
       </c>
       <c r="N5" s="1">
-        <v>-12.6</v>
+        <v>-11.8</v>
       </c>
       <c r="O5" s="1">
-        <v>-28.3</v>
+        <v>-27.5</v>
       </c>
       <c r="P5" s="1">
-        <v>-28.3</v>
+        <v>-27.5</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0331</v>
@@ -832,28 +832,28 @@
         <v>10</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0054</v>
+        <v>0.0067</v>
       </c>
       <c r="U5" s="5">
-        <v>4.834</v>
+        <v>4.84</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0254</v>
+        <v>0.0242</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0121</v>
+        <v>0.0134</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0349</v>
+        <v>0.0362</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0866</v>
+        <v>0.088</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2619</v>
+        <v>0.2635</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>946.2</v>
+        <v>945.7</v>
       </c>
       <c r="D6" s="1">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0013</v>
+        <v>0.0007</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-27.5</v>
+        <v>-28</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0282</v>
+        <v>-0.0288</v>
       </c>
       <c r="L6" s="1">
-        <v>-27.5</v>
+        <v>-28</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0282</v>
+        <v>-0.0288</v>
       </c>
       <c r="N6" s="1">
-        <v>-10.8</v>
+        <v>-10.5</v>
       </c>
       <c r="O6" s="1">
-        <v>-29.1</v>
+        <v>-28.8</v>
       </c>
       <c r="P6" s="1">
-        <v>-29.1</v>
+        <v>-28.8</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0324</v>
+        <v>0.0323</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>10</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0013</v>
+        <v>0.0007</v>
       </c>
       <c r="U6" s="5">
-        <v>9.462</v>
+        <v>9.457</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0291</v>
+        <v>0.0296</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0547</v>
+        <v>-0.0552</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1053</v>
+        <v>-0.1057</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0719</v>
+        <v>0.0713</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2719</v>
+        <v>0.2712</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1032</v>
+        <v>0.1031</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1063,13 +1063,13 @@
         <v>-0.0047</v>
       </c>
       <c r="N8" s="1">
-        <v>-17</v>
+        <v>-15.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-9.7</v>
+        <v>-8.3</v>
       </c>
       <c r="P8" s="1">
-        <v>-9.7</v>
+        <v>-8.3</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0268</v>
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19801.6</v>
+        <v>19818.4</v>
       </c>
       <c r="D9" s="1">
-        <v>53.2</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0027</v>
+        <v>0.0035</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-576.04</v>
+        <v>-559.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0283</v>
+        <v>-0.0274</v>
       </c>
       <c r="L9" s="1">
-        <v>-576.04</v>
+        <v>-559.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0283</v>
+        <v>-0.0274</v>
       </c>
       <c r="N9" s="1">
-        <v>1.4</v>
+        <v>25.2</v>
       </c>
       <c r="O9" s="1">
-        <v>-608.24</v>
+        <v>-584.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-608.24</v>
+        <v>-584.44</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6771</v>
@@ -1164,28 +1164,28 @@
         <v>10</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0027</v>
+        <v>0.0035</v>
       </c>
       <c r="U9" s="5">
-        <v>14.144</v>
+        <v>14.156</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0291</v>
+        <v>0.0282</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0093</v>
+        <v>-0.0085</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0325</v>
+        <v>-0.0317</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0503</v>
+        <v>0.0512</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1718</v>
+        <v>0.1728</v>
       </c>
     </row>
     <row r="10">
@@ -1229,13 +1229,13 @@
         <v>-0.0376</v>
       </c>
       <c r="N10" s="1">
-        <v>-11.6</v>
+        <v>-11.2</v>
       </c>
       <c r="O10" s="1">
-        <v>-24.1</v>
+        <v>-23.7</v>
       </c>
       <c r="P10" s="1">
-        <v>-24.1</v>
+        <v>-23.7</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0221</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>859.2</v>
+        <v>860</v>
       </c>
       <c r="D11" s="1">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="E11" s="2">
-        <v>0.008</v>
+        <v>0.0089</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0006</v>
       </c>
       <c r="L11" s="1">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0006</v>
       </c>
       <c r="N11" s="1">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O11" s="1">
-        <v>-3.3</v>
+        <v>-3.7</v>
       </c>
       <c r="P11" s="1">
-        <v>-3.3</v>
+        <v>-3.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0294</v>
@@ -1330,28 +1330,28 @@
         <v>10</v>
       </c>
       <c r="T11" s="2">
-        <v>0.008</v>
+        <v>0.0089</v>
       </c>
       <c r="U11" s="5">
-        <v>2.148</v>
+        <v>2.15</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0014</v>
+        <v>0.0005</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0224</v>
+        <v>0.0233</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0468</v>
+        <v>0.0478</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2027</v>
+        <v>0.2038</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2778</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29239.8</v>
+        <v>29263.6</v>
       </c>
       <c r="D12" s="1">
-        <v>70.5</v>
+        <v>94.3</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0024</v>
+        <v>0.0032</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-751.99</v>
+        <v>-728.19</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0251</v>
+        <v>-0.0243</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-81.5</v>
+        <v>-56.3</v>
       </c>
       <c r="O12" s="1">
-        <v>-799.89</v>
+        <v>-774.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-799.89</v>
+        <v>-774.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9999</v>

--- a/组合实盘追踪/20260522_银河.xlsx
+++ b/组合实盘追踪/20260522_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>694.6</v>
+        <v>689.2</v>
       </c>
       <c r="D2" s="1">
-        <v>8.2</v>
+        <v>2.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0119</v>
+        <v>0.0041</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-16.5</v>
+        <v>-21.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0308</v>
       </c>
       <c r="L2" s="1">
-        <v>-16.5</v>
+        <v>-21.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0232</v>
+        <v>-0.0308</v>
       </c>
       <c r="N2" s="1">
-        <v>-7.6</v>
+        <v>-8.6</v>
       </c>
       <c r="O2" s="1">
-        <v>-21.1</v>
+        <v>-22.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-21.1</v>
+        <v>-22.1</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0237</v>
+        <v>0.0236</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>10</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0119</v>
+        <v>0.0041</v>
       </c>
       <c r="U2" s="5">
-        <v>3.473</v>
+        <v>3.446</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0239</v>
+        <v>0.0319</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0386</v>
+        <v>0.0305</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0572</v>
+        <v>0.049</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2286</v>
+        <v>0.2191</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4311</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="3">
@@ -648,13 +648,13 @@
         <v>-0.0381</v>
       </c>
       <c r="N3" s="1">
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="O3" s="1">
-        <v>-32.9</v>
+        <v>-33.3</v>
       </c>
       <c r="P3" s="1">
-        <v>-32.9</v>
+        <v>-33.3</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>698.5</v>
+        <v>696.3</v>
       </c>
       <c r="D4" s="1">
-        <v>8.8</v>
+        <v>6.6</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0128</v>
+        <v>0.0096</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-38.6</v>
+        <v>-40.8</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0524</v>
+        <v>-0.0554</v>
       </c>
       <c r="L4" s="1">
-        <v>-38.6</v>
+        <v>-40.8</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0524</v>
+        <v>-0.0554</v>
       </c>
       <c r="N4" s="1">
-        <v>-20.9</v>
+        <v>-18.7</v>
       </c>
       <c r="O4" s="1">
-        <v>-44.1</v>
+        <v>-41.9</v>
       </c>
       <c r="P4" s="1">
-        <v>-44.1</v>
+        <v>-41.9</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0239</v>
+        <v>0.0238</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>10</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0128</v>
+        <v>0.0096</v>
       </c>
       <c r="U4" s="5">
-        <v>0.635</v>
+        <v>0.633</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0551</v>
+        <v>0.0585</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0466</v>
+        <v>-0.0496</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1217</v>
+        <v>-0.1245</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1544</v>
+        <v>-0.1571</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1384</v>
+        <v>-0.1412</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>968</v>
+        <v>965.2</v>
       </c>
       <c r="D5" s="1">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0067</v>
+        <v>0.0037</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-23.3</v>
+        <v>-26.1</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0235</v>
+        <v>-0.0263</v>
       </c>
       <c r="L5" s="1">
-        <v>-23.3</v>
+        <v>-26.1</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0235</v>
+        <v>-0.0263</v>
       </c>
       <c r="N5" s="1">
-        <v>-11.8</v>
+        <v>-12.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-27.5</v>
+        <v>-28.1</v>
       </c>
       <c r="P5" s="1">
-        <v>-27.5</v>
+        <v>-28.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0331</v>
+        <v>0.033</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>10</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0067</v>
+        <v>0.0037</v>
       </c>
       <c r="U5" s="5">
-        <v>4.84</v>
+        <v>4.826</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0242</v>
+        <v>0.0271</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0134</v>
+        <v>0.0105</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0362</v>
+        <v>0.0332</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.088</v>
+        <v>0.0848</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2635</v>
+        <v>0.2598</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>945.7</v>
+        <v>944.7</v>
       </c>
       <c r="D6" s="1">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0288</v>
+        <v>-0.0298</v>
       </c>
       <c r="L6" s="1">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0288</v>
+        <v>-0.0298</v>
       </c>
       <c r="N6" s="1">
-        <v>-10.5</v>
+        <v>-9.9</v>
       </c>
       <c r="O6" s="1">
-        <v>-28.8</v>
+        <v>-28.2</v>
       </c>
       <c r="P6" s="1">
-        <v>-28.8</v>
+        <v>-28.2</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0323</v>
@@ -915,28 +915,28 @@
         <v>10</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="U6" s="5">
-        <v>9.457</v>
+        <v>9.447</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0296</v>
+        <v>0.0307</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0552</v>
+        <v>-0.0562</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1057</v>
+        <v>-0.1067</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0713</v>
+        <v>0.0702</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2712</v>
+        <v>0.2699</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1031</v>
+        <v>0.1034</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>783</v>
+        <v>778.6</v>
       </c>
       <c r="D8" s="1">
-        <v>13.8</v>
+        <v>9.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0179</v>
+        <v>0.0122</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-3.7</v>
+        <v>-8.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0047</v>
+        <v>-0.0103</v>
       </c>
       <c r="L8" s="1">
-        <v>-3.7</v>
+        <v>-8.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0047</v>
+        <v>-0.0103</v>
       </c>
       <c r="N8" s="1">
-        <v>-15.6</v>
+        <v>-18</v>
       </c>
       <c r="O8" s="1">
-        <v>-8.3</v>
+        <v>-10.7</v>
       </c>
       <c r="P8" s="1">
-        <v>-8.3</v>
+        <v>-10.7</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0268</v>
+        <v>0.0267</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,28 +1081,28 @@
         <v>10</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0179</v>
+        <v>0.0122</v>
       </c>
       <c r="U8" s="5">
-        <v>3.915</v>
+        <v>3.893</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0049</v>
+        <v>0.0105</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0635</v>
+        <v>0.0576</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.199</v>
+        <v>0.1923</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3482</v>
+        <v>0.3406</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9248</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19818.4</v>
+        <v>19770.8</v>
       </c>
       <c r="D9" s="1">
-        <v>70</v>
+        <v>22.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0035</v>
+        <v>0.0011</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-559.24</v>
+        <v>-606.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0274</v>
+        <v>-0.0298</v>
       </c>
       <c r="L9" s="1">
-        <v>-559.24</v>
+        <v>-606.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0274</v>
+        <v>-0.0298</v>
       </c>
       <c r="N9" s="1">
-        <v>25.2</v>
+        <v>-15.4</v>
       </c>
       <c r="O9" s="1">
-        <v>-584.44</v>
+        <v>-625.04</v>
       </c>
       <c r="P9" s="1">
-        <v>-584.44</v>
+        <v>-625.04</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6771</v>
+        <v>0.6769</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>10</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0035</v>
+        <v>0.0011</v>
       </c>
       <c r="U9" s="5">
-        <v>14.156</v>
+        <v>14.122</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0282</v>
+        <v>0.0307</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0085</v>
+        <v>-0.0109</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0317</v>
+        <v>-0.034</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0512</v>
+        <v>0.0487</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1728</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="10">
@@ -1279,46 +1279,46 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>860</v>
+        <v>858.4</v>
       </c>
       <c r="D11" s="1">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.007</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" s="2">
+        <v/>
+      </c>
+      <c r="H11" s="1">
+        <v/>
+      </c>
+      <c r="I11" s="2">
+        <v/>
+      </c>
+      <c r="J11" s="1">
+        <v>-2.1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>-0.0024</v>
+      </c>
+      <c r="L11" s="1">
+        <v>-2.1</v>
+      </c>
+      <c r="M11" s="2">
+        <v>-0.0024</v>
+      </c>
+      <c r="N11" s="1">
         <v>7.6</v>
       </c>
-      <c r="E11" s="2">
-        <v>0.0089</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" s="2">
-        <v/>
-      </c>
-      <c r="H11" s="1">
-        <v/>
-      </c>
-      <c r="I11" s="2">
-        <v/>
-      </c>
-      <c r="J11" s="1">
+      <c r="O11" s="1">
         <v>-0.5</v>
       </c>
-      <c r="K11" s="2">
-        <v>-0.0006</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="P11" s="1">
         <v>-0.5</v>
-      </c>
-      <c r="M11" s="2">
-        <v>-0.0006</v>
-      </c>
-      <c r="N11" s="1">
-        <v>4.4</v>
-      </c>
-      <c r="O11" s="1">
-        <v>-3.7</v>
-      </c>
-      <c r="P11" s="1">
-        <v>-3.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0294</v>
@@ -1330,28 +1330,28 @@
         <v>10</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0089</v>
+        <v>0.007</v>
       </c>
       <c r="U11" s="5">
-        <v>2.15</v>
+        <v>2.146</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0005</v>
+        <v>0.0023</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0233</v>
+        <v>0.0214</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0478</v>
+        <v>0.0458</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2038</v>
+        <v>0.2016</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.279</v>
+        <v>0.2766</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29263.6</v>
+        <v>29198.6</v>
       </c>
       <c r="D12" s="1">
-        <v>94.3</v>
+        <v>29.3</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0032</v>
+        <v>0.001</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-728.19</v>
+        <v>-793.19</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0243</v>
+        <v>-0.0264</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,16 +1395,16 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-56.3</v>
+        <v>-95.3</v>
       </c>
       <c r="O12" s="1">
-        <v>-774.69</v>
+        <v>-813.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-774.69</v>
+        <v>-813.69</v>
       </c>
       <c r="Q12" s="2">
-        <v>0.9999</v>
+        <v>0.9997</v>
       </c>
       <c r="R12" t="str">
         <v/>

--- a/组合实盘追踪/20260522_银河.xlsx
+++ b/组合实盘追踪/20260522_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>689.2</v>
+        <v>695</v>
       </c>
       <c r="D2" s="1">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0041</v>
+        <v>0.0125</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-21.9</v>
+        <v>-16.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0308</v>
+        <v>-0.0226</v>
       </c>
       <c r="L2" s="1">
-        <v>-21.9</v>
+        <v>-16.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0308</v>
+        <v>-0.0226</v>
       </c>
       <c r="N2" s="1">
-        <v>-8.6</v>
+        <v>-2.6</v>
       </c>
       <c r="O2" s="1">
-        <v>-22.1</v>
+        <v>-16.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-22.1</v>
+        <v>-16.1</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0236</v>
+        <v>0.0238</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>10</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0041</v>
+        <v>0.0125</v>
       </c>
       <c r="U2" s="5">
-        <v>3.446</v>
+        <v>3.475</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0319</v>
+        <v>0.0233</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0305</v>
+        <v>0.0392</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.049</v>
+        <v>0.0578</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.2191</v>
+        <v>0.2293</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.42</v>
+        <v>0.4319</v>
       </c>
     </row>
     <row r="3">
@@ -615,46 +615,46 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>830</v>
+        <v>831.2</v>
       </c>
       <c r="D3" s="1">
+        <v>-3.2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>-0.0038</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <v/>
+      </c>
+      <c r="H3" s="1">
+        <v/>
+      </c>
+      <c r="I3" s="2">
+        <v/>
+      </c>
+      <c r="J3" s="1">
+        <v>-31.7</v>
+      </c>
+      <c r="K3" s="2">
+        <v>-0.0367</v>
+      </c>
+      <c r="L3" s="1">
+        <v>-31.7</v>
+      </c>
+      <c r="M3" s="2">
+        <v>-0.0367</v>
+      </c>
+      <c r="N3" s="1">
         <v>-4.4</v>
       </c>
-      <c r="E3" s="2">
-        <v>-0.0053</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" s="2">
-        <v/>
-      </c>
-      <c r="H3" s="1">
-        <v/>
-      </c>
-      <c r="I3" s="2">
-        <v/>
-      </c>
-      <c r="J3" s="1">
-        <v>-32.9</v>
-      </c>
-      <c r="K3" s="2">
-        <v>-0.0381</v>
-      </c>
-      <c r="L3" s="1">
-        <v>-32.9</v>
-      </c>
-      <c r="M3" s="2">
-        <v>-0.0381</v>
-      </c>
-      <c r="N3" s="1">
-        <v>-6</v>
-      </c>
       <c r="O3" s="1">
-        <v>-33.3</v>
+        <v>-31.7</v>
       </c>
       <c r="P3" s="1">
-        <v>-33.3</v>
+        <v>-31.7</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -666,28 +666,28 @@
         <v>10</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0053</v>
+        <v>-0.0038</v>
       </c>
       <c r="U3" s="5">
-        <v>2.075</v>
+        <v>2.078</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0395</v>
+        <v>0.038</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0245</v>
+        <v>-0.0231</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0375</v>
+        <v>0.039</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0495</v>
+        <v>0.0511</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0746</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>696.3</v>
+        <v>699.6</v>
       </c>
       <c r="D4" s="1">
-        <v>6.6</v>
+        <v>9.9</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0096</v>
+        <v>0.0144</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0554</v>
+        <v>-0.0509</v>
       </c>
       <c r="L4" s="1">
-        <v>-40.8</v>
+        <v>-37.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0554</v>
+        <v>-0.0509</v>
       </c>
       <c r="N4" s="1">
-        <v>-18.7</v>
+        <v>-14.3</v>
       </c>
       <c r="O4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="P4" s="1">
-        <v>-41.9</v>
+        <v>-37.5</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0238</v>
+        <v>0.0239</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>10</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0096</v>
+        <v>0.0144</v>
       </c>
       <c r="U4" s="5">
-        <v>0.633</v>
+        <v>0.636</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0585</v>
+        <v>0.0535</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0496</v>
+        <v>-0.0451</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1245</v>
+        <v>-0.1204</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1571</v>
+        <v>-0.1531</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1412</v>
+        <v>-0.1371</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>965.2</v>
+        <v>967</v>
       </c>
       <c r="D5" s="1">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0037</v>
+        <v>0.0056</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-26.1</v>
+        <v>-24.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0263</v>
+        <v>-0.0245</v>
       </c>
       <c r="L5" s="1">
-        <v>-26.1</v>
+        <v>-24.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0263</v>
+        <v>-0.0245</v>
       </c>
       <c r="N5" s="1">
-        <v>-12.4</v>
+        <v>-8.6</v>
       </c>
       <c r="O5" s="1">
-        <v>-28.1</v>
+        <v>-24.3</v>
       </c>
       <c r="P5" s="1">
-        <v>-28.1</v>
+        <v>-24.3</v>
       </c>
       <c r="Q5" s="2">
         <v>0.033</v>
@@ -832,28 +832,28 @@
         <v>10</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0037</v>
+        <v>0.0056</v>
       </c>
       <c r="U5" s="5">
-        <v>4.826</v>
+        <v>4.835</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0271</v>
+        <v>0.0252</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0105</v>
+        <v>0.0124</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0332</v>
+        <v>0.0351</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0848</v>
+        <v>0.0869</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2598</v>
+        <v>0.2621</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>944.7</v>
+        <v>944.8</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" s="2">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-29</v>
+        <v>-28.9</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0298</v>
+        <v>-0.0297</v>
       </c>
       <c r="L6" s="1">
-        <v>-29</v>
+        <v>-28.9</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0298</v>
+        <v>-0.0297</v>
       </c>
       <c r="N6" s="1">
-        <v>-9.9</v>
+        <v>-10.6</v>
       </c>
       <c r="O6" s="1">
-        <v>-28.2</v>
+        <v>-28.9</v>
       </c>
       <c r="P6" s="1">
-        <v>-28.2</v>
+        <v>-28.9</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0323</v>
@@ -915,28 +915,28 @@
         <v>10</v>
       </c>
       <c r="T6" s="2">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="U6" s="5">
-        <v>9.447</v>
+        <v>9.448</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0307</v>
+        <v>0.0306</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0562</v>
+        <v>-0.0561</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1067</v>
+        <v>-0.1066</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0702</v>
+        <v>0.0703</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2699</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1034</v>
+        <v>0.1032</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>778.6</v>
+        <v>782.6</v>
       </c>
       <c r="D8" s="1">
-        <v>9.4</v>
+        <v>13.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0122</v>
+        <v>0.0174</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-8.1</v>
+        <v>-4.1</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0103</v>
+        <v>-0.0052</v>
       </c>
       <c r="L8" s="1">
-        <v>-8.1</v>
+        <v>-4.1</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0103</v>
+        <v>-0.0052</v>
       </c>
       <c r="N8" s="1">
-        <v>-18</v>
+        <v>-11.4</v>
       </c>
       <c r="O8" s="1">
-        <v>-10.7</v>
+        <v>-4.1</v>
       </c>
       <c r="P8" s="1">
-        <v>-10.7</v>
+        <v>-4.1</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0267</v>
@@ -1081,28 +1081,28 @@
         <v>10</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0122</v>
+        <v>0.0174</v>
       </c>
       <c r="U8" s="5">
-        <v>3.893</v>
+        <v>3.913</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0105</v>
+        <v>0.0054</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0576</v>
+        <v>0.063</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.1923</v>
+        <v>0.1984</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3406</v>
+        <v>0.3475</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.914</v>
+        <v>0.9238</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19770.8</v>
+        <v>19812.8</v>
       </c>
       <c r="D9" s="1">
-        <v>22.4</v>
+        <v>64.4</v>
       </c>
       <c r="E9" s="2">
-        <v>0.0011</v>
+        <v>0.0033</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-606.84</v>
+        <v>-564.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0298</v>
+        <v>-0.0277</v>
       </c>
       <c r="L9" s="1">
-        <v>-606.84</v>
+        <v>-564.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0298</v>
+        <v>-0.0277</v>
       </c>
       <c r="N9" s="1">
-        <v>-15.4</v>
+        <v>44.8</v>
       </c>
       <c r="O9" s="1">
-        <v>-625.04</v>
+        <v>-564.84</v>
       </c>
       <c r="P9" s="1">
-        <v>-625.04</v>
+        <v>-564.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6769</v>
+        <v>0.6771</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>10</v>
       </c>
       <c r="T9" s="2">
-        <v>0.0011</v>
+        <v>0.0033</v>
       </c>
       <c r="U9" s="5">
-        <v>14.122</v>
+        <v>14.152</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0307</v>
+        <v>0.0285</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0109</v>
+        <v>-0.0088</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.034</v>
+        <v>-0.032</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0487</v>
+        <v>0.0509</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.17</v>
+        <v>0.1725</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>646.8</v>
+        <v>643.6</v>
       </c>
       <c r="D10" s="1">
-        <v>-16.8</v>
+        <v>-20</v>
       </c>
       <c r="E10" s="2">
-        <v>-0.0253</v>
+        <v>-0.0301</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-25.3</v>
+        <v>-28.5</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0376</v>
+        <v>-0.0424</v>
       </c>
       <c r="L10" s="1">
-        <v>-25.3</v>
+        <v>-28.5</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0376</v>
+        <v>-0.0424</v>
       </c>
       <c r="N10" s="1">
-        <v>-11.2</v>
+        <v>-16</v>
       </c>
       <c r="O10" s="1">
-        <v>-23.7</v>
+        <v>-28.5</v>
       </c>
       <c r="P10" s="1">
-        <v>-23.7</v>
+        <v>-28.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0221</v>
+        <v>0.022</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>10</v>
       </c>
       <c r="T10" s="2">
-        <v>-0.0253</v>
+        <v>-0.0301</v>
       </c>
       <c r="U10" s="5">
-        <v>1.617</v>
+        <v>1.609</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.039</v>
+        <v>0.0441</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.008</v>
+        <v>-0.0129</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2742</v>
+        <v>0.2679</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3566</v>
+        <v>0.3499</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2306</v>
+        <v>0.2245</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>858.4</v>
+        <v>859.2</v>
       </c>
       <c r="D11" s="1">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="E11" s="2">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="L11" s="1">
-        <v>-2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0024</v>
+        <v>-0.0015</v>
       </c>
       <c r="N11" s="1">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0294</v>
@@ -1330,28 +1330,28 @@
         <v>10</v>
       </c>
       <c r="T11" s="2">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="U11" s="5">
-        <v>2.146</v>
+        <v>2.148</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0023</v>
+        <v>0.0014</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0214</v>
+        <v>0.0224</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0458</v>
+        <v>0.0468</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2016</v>
+        <v>0.2027</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2766</v>
+        <v>0.2778</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29198.6</v>
+        <v>29254.4</v>
       </c>
       <c r="D12" s="1">
-        <v>29.3</v>
+        <v>85.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0.001</v>
+        <v>0.0029</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-793.19</v>
+        <v>-737.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0264</v>
+        <v>-0.0246</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-95.3</v>
+        <v>-19</v>
       </c>
       <c r="O12" s="1">
-        <v>-813.69</v>
+        <v>-737.39</v>
       </c>
       <c r="P12" s="1">
-        <v>-813.69</v>
+        <v>-737.39</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>
